--- a/文档/本地化修正/引言.xlsx
+++ b/文档/本地化修正/引言.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
     <t>LOC_FEATURE_VESUVIUS_QUOTE</t>
   </si>
   <si>
-    <t>“大海在向后退缩，好像是被大地的震动推了回去;海岸则明显地向前延伸，许多海生动物搁浅在沙滩上。在海岸的那一面，浓云密布，乌黑可怕，蜿蜒的火舌不停地晃动着，火的势浪冲击着云层，把云层撕裂，状如火焰本身…”[NEWLINE]——小普林尼</t>
+    <t>“大海在向后退缩，好像是被大地的震动推了回去；海岸则明显地向前延伸，许多海生动物搁浅在沙滩上。在海岸的那一面，浓云密布，乌黑可怕，蜿蜒的火舌不停地晃动着，火的势浪冲击着云层，把云层撕裂，状如火焰本身…”[NEWLINE]——小普林尼</t>
   </si>
   <si>
     <t>注：英文文本似乎翻译有误。</t>
@@ -2183,7 +2183,7 @@
     <t>LOC_BUILDING_AMUNDSEN_SCOTT_RESEARCH_STATION_QUOTE</t>
   </si>
   <si>
-    <t>论科学领导力，斯科特首屈一指；而论行进之迅速高效，阿蒙森当仁不让。[NEWLINE]——雷蒙德·普里斯特利爵士</t>
+    <t>“论科学领导力，斯科特首屈一指；而论行进之迅速高效，阿蒙森当仁不让。”[NEWLINE]——雷蒙德·普里斯特利爵士</t>
   </si>
   <si>
     <t>LOC_BUILDING_CASA_DE_CONTRATACION_QUOTE</t>
@@ -3278,10 +3278,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="80.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="228.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" spans="1:3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_CLIFFS_DOVER_QUOTE" Language="zh_Hans_CN" Text="“在白崖城垛般的平顶下，一片胜过安息日的寂静。”[NEWLINE]——威廉·华兹华斯"/&gt;</v>
       </c>
     </row>
-    <row r="3" ht="33" spans="1:3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_GALAPAGOS_QUOTE" Language="zh_Hans_CN" Text="“这个群岛的自然历史非常奇特：它好像自成一个小世界。”[NEWLINE]——查尔斯·达尔文"/&gt;</v>
       </c>
     </row>
-    <row r="7" ht="33" spans="1:3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_KILIMANJARO_QUOTE" Language="zh_Hans_CN" Text="“结果，乞力马扎罗山上没有 Wi-Fi，所以旅行途中我只好在坦桑尼亚和人聊天度过两周时光。”[NEWLINE]——南希·邦兹"/&gt;</v>
       </c>
     </row>
-    <row r="8" ht="33" spans="1:3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_PANTANAL_QUOTE" Language="zh_Hans_CN" Text="“潘塔纳尔湿地是世界上最复杂的热带冲积平原，可能也是最不为人所知的地方。”[NEWLINE]——阿齐兹·萨比尔"/&gt;</v>
       </c>
     </row>
-    <row r="9" ht="33" spans="1:3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_PIOPIOTAHI_QUOTE" Language="zh_Hans_CN" Text="“但，当我进入新西兰峡湾中心时，久违的，孩童般的纯粹十足的敬畏感涌回我的心底。我听闻过通往米尔福德峡湾的道路景色很美——但怎会如此美丽？”[NEWLINE]——达罗克·唐纳德"/&gt;</v>
       </c>
     </row>
-    <row r="10" ht="33" spans="1:3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_TORRES_DEL_PAINE_QUOTE" Language="zh_Hans_CN" Text="“几座坐落在一起的花冈岩峰像老虎的牙齿一样，高约一千米，耸入天空。”[NEWLINE]——霍华德·希尔曼"/&gt;</v>
       </c>
     </row>
-    <row r="11" ht="33" spans="1:3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_TSINGY_QUOTE" Language="zh_Hans_CN" Text="“黥基石林是个占地647平方千米的老虎陷阱，由巨大的方尖碑组成，其中布满了锯齿状的尖头。是的，它们会将你的漂亮脸蛋刺破。”[NEWLINE]——巴德·埃里克森"/&gt;</v>
       </c>
     </row>
-    <row r="12" ht="33" spans="1:3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_ULURU_QUOTE" Language="zh_Hans_CN" Text="“雨季时这里景色该有多壮丽啊，四面八方都是瀑布！”[NEWLINE]——威廉·高斯"/&gt;</v>
       </c>
     </row>
-    <row r="14" ht="33" spans="1:3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_DELICATE_ARCH_QUOTE" Language="zh_Hans_CN" Text="“若精致拱门蕴含深意，我将深入探索奥妙。其中自然之力怪奇无比，颠覆世人之常态感观。”[NEWLINE]——爱德华·艾比"/&gt;</v>
       </c>
     </row>
-    <row r="15" ht="33" spans="1:3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_EYE_OF_THE_SAHARA_QUOTE" Language="zh_Hans_CN" Text="“奇怪的是，它看起来不似陨石撞击所致，而更像深度侵蚀形成的穹丘。颜色搭配则酷似彩虹。”——克里斯·哈德菲尔"/&gt;</v>
       </c>
     </row>
-    <row r="16" ht="33" spans="1:3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_MATTERHORN_QUOTE" Language="zh_Hans_CN" Text="“容我转身离去，赶在最后一丝金色残阳离开它的峰巅前往更加高远的地方之前，为曾经向往的马特洪峰献出由衷的尊敬和赞美。”[NEWLINE]——F.克劳福德·格罗夫"/&gt;</v>
       </c>
     </row>
-    <row r="17" ht="33" spans="1:4">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -3509,7 +3509,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_LAKE_RETBA_QUOTE" Language="zh_Hans_CN" Text="“四下皆水，然决不可饮。”[NEWLINE]——塞缪尔·泰勒·柯勒律治《古舟子咏》"/&gt;</v>
       </c>
     </row>
-    <row r="20" ht="49.5" spans="1:4">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_CHOCOLATEHILLS_QUOTE" Language="zh_Hans_CN" Text="“邪恶的国王骑着他最快的马匹，追赶着爱侣胡安与玛利亚。在他即将追上他们时，玛利亚将她的戒指抛向地面。七座巨人般高大的山丘随即冲破地面，国王不得不放缓追逐的脚步。”[NEWLINE]——菲律宾民间传说"/&gt;</v>
       </c>
     </row>
-    <row r="21" ht="49.5" spans="1:4">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_DEVILSTOWER_QUOTE" Language="zh_Hans_CN" Text="“七名少女正被熊群追逐。正当熊快要追上她们时，少女们跳上了一块低矮的岩石。一名少女向岩石祈祷道：岩石啊，怜悯我们吧，救救我们吧！岩石听见了她们的祈祷，随即拔地而起，将少女们送上高处。”[NEWLINE]——基奥瓦传说"/&gt;</v>
       </c>
     </row>
-    <row r="22" ht="33" spans="1:4">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_GOBUSTAN_QUOTE" Language="zh_Hans_CN" Text="“那么快张起神秘的罗网；[NEWLINE]啊，力量与欢愉的玲珑精灵，[NEWLINE]快从地角和天边走来，[NEWLINE]让曼舞和欢歌满布这世间。”[NEWLINE]——珀西·比希·雪莱"/&gt;</v>
       </c>
     </row>
-    <row r="23" ht="33" spans="1:4">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_IKKIL_QUOTE" Language="zh_Hans_CN" Text="“孩子，你见过天神之雨吗？雨水落下，浸入天神之山…天空中将出现一道圆环，天神之水便会从中缓缓流出。”[NEWLINE]——《契伦巴伦之书》"/&gt;</v>
       </c>
     </row>
-    <row r="24" ht="49.5" spans="1:4">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_PAMUKKALE_QUOTE" Language="zh_Hans_CN" Text="“在美索吉旁，与劳迪希亚相对的便是希拉波利斯古城，那里盛产温泉，还有一座冥王神殿，两者皆有非凡性质。这里的泉水十分容易沉积为岩石，通过水道进行引导后，便会形成一整片石堤。”[NEWLINE]——斯特拉波"/&gt;</v>
       </c>
     </row>
-    <row r="25" ht="49.5" spans="1:4">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -3578,13 +3578,13 @@
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
-        <v>&lt;Replace Tag="LOC_FEATURE_VESUVIUS_QUOTE" Language="zh_Hans_CN" Text="“大海在向后退缩，好像是被大地的震动推了回去;海岸则明显地向前延伸，许多海生动物搁浅在沙滩上。在海岸的那一面，浓云密布，乌黑可怕，蜿蜒的火舌不停地晃动着，火的势浪冲击着云层，把云层撕裂，状如火焰本身…”[NEWLINE]——小普林尼"/&gt;</v>
+        <v>&lt;Replace Tag="LOC_FEATURE_VESUVIUS_QUOTE" Language="zh_Hans_CN" Text="“大海在向后退缩，好像是被大地的震动推了回去；海岸则明显地向前延伸，许多海生动物搁浅在沙滩上。在海岸的那一面，浓云密布，乌黑可怕，蜿蜒的火舌不停地晃动着，火的势浪冲击着云层，把云层撕裂，状如火焰本身…”[NEWLINE]——小普林尼"/&gt;</v>
       </c>
       <c r="D25" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="33" spans="1:4">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" ht="49.5" spans="1:4">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>53</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_BERMUDA_TRIANGLE_QUOTE" Language="zh_Hans_CN" Text="“无人知晓这片海洋有着怎样美妙的神秘之处，它那不怒而威的波动起伏似乎在表明下面有着深藏不露的灵魂…无数幻影幽灵、沉迷的梦想家、梦游者、幻梦者，以及一切我们称之为生命与灵魂的，都在这里做梦，做梦，一直做下去。”[NEWLINE]——赫尔曼·梅尔维尔"/&gt;</v>
       </c>
     </row>
-    <row r="28" ht="33" spans="1:4">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_PAITITI_QUOTE" Language="zh_Hans_CN" Text="“如未开采的黄金一般，隐藏在枝繁叶茂的旷野之中。”[NEWLINE]——约翰·缪尔"/&gt;</v>
       </c>
     </row>
-    <row r="30" ht="33" spans="1:4">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" ht="33" spans="1:4">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -3662,7 +3662,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_EYJAFJALLAJOKULL_QUOTE" Language="zh_Hans_CN" Text="“高耸的巨大火柱照亮了大地，使霍尔特的夜晚亮如白昼，足以阅读。”[NEWLINE]——《利物浦水星报》"/&gt;</v>
       </c>
     </row>
-    <row r="32" ht="33" spans="1:4">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_GIANTS_CAUSEWAY_QUOTE" Language="zh_Hans_CN" Text="“这里有深棕色的非晶玄武岩和红色的赭石，下面则又是分界清晰的薄木炭层。”[NEWLINE]——《都柏林便士杂志》"/&gt;</v>
       </c>
     </row>
-    <row r="33" ht="33" spans="1:3">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -3686,7 +3686,7 @@
         <v>&lt;Replace Tag="LOC_FEATURE_LYSEFJORDEN_QUOTE" Language="zh_Hans_CN" Text="“在这片海和无尽的孤独中出现了一条昏暗的道路，一条没有人类足迹的道路。没有人曾经过此地；亦没有船只曾在此航行。”[NEWLINE]——维克多·雨果"/&gt;</v>
       </c>
     </row>
-    <row r="34" ht="33" spans="1:3">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>&lt;Replace Tag="LOC_TECH_IRRIGATION_QUOTE_1" Language="zh_Hans_CN" Text="“千万人没有爱也能活着，但没有人没有水还能活着。”[NEWLINE]——威斯坦·休·奥登"/&gt;</v>
       </c>
     </row>
-    <row r="45" ht="33" spans="1:3">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>&lt;Replace Tag="LOC_TECH_ARCHERY_QUOTE_2" Language="zh_Hans_CN" Text="“愿你射箭之时，邪恶不知所措。”[NEWLINE]——乔治·卡林"/&gt;</v>
       </c>
     </row>
-    <row r="48" ht="33" spans="1:3">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>95</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>&lt;Replace Tag="LOC_TECH_WRITING_QUOTE_2" Language="zh_Hans_CN" Text="“写作很简单。你只要把写错的词划掉。”[NEWLINE]——马克·吐温"/&gt;</v>
       </c>
     </row>
-    <row r="50" ht="33" spans="1:3">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>99</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>&lt;Replace Tag="LOC_TECH_BRONZE_WORKING_QUOTE_1" Language="zh_Hans_CN" Text="“青铜是有形之物的明镜，是滋润心灵的美酒。”[NEWLINE]——埃斯库罗斯"/&gt;</v>
       </c>
     </row>
-    <row r="53" ht="33" spans="1:3">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -3962,7 +3962,7 @@
         <v>&lt;Replace Tag="LOC_TECH_CELESTIAL_NAVIGATION_QUOTE_1" Language="zh_Hans_CN" Text="“我要的只有一艘高高的船，还有一颗星星为我导航。”[NEWLINE]——约翰·梅斯菲尔德"/&gt;</v>
       </c>
     </row>
-    <row r="57" ht="33" spans="1:3">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>113</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>&lt;Replace Tag="LOC_TECH_HORSEBACK_RIDING_QUOTE_2" Language="zh_Hans_CN" Text="“骑马的人在精神和体格方面都比走路的人强。”[NEWLINE]——约翰·斯坦贝克"/&gt;</v>
       </c>
     </row>
-    <row r="62" ht="33" spans="1:3">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>123</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>&lt;Replace Tag="LOC_TECH_IRON_WORKING_QUOTE_2" Language="zh_Hans_CN" Text="“万物都有极限——铁矿石不可能被打造成黄金。”[NEWLINE]——马克·吐温"/&gt;</v>
       </c>
     </row>
-    <row r="64" ht="33" spans="1:3">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>127</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SHIPBUILDING_QUOTE_2" Language="zh_Hans_CN" Text="“在水手和来世之间除了块厚木板，什么也没有。”[NEWLINE]——汤姆斯·吉本斯"/&gt;</v>
       </c>
     </row>
-    <row r="66" ht="33" spans="1:3">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>&lt;Replace Tag="LOC_TECH_MATHEMATICS_QUOTE_1" Language="zh_Hans_CN" Text="“没有数学，你什么也做不了。你周围的一切都是数学。你周围的一切都是数字。”[NEWLINE]——夏琨塔拉·戴维"/&gt;</v>
       </c>
     </row>
-    <row r="67" ht="33" spans="1:3">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -4130,7 +4130,7 @@
         <v>&lt;Replace Tag="LOC_TECH_ENGINEERING_QUOTE_1" Language="zh_Hans_CN" Text="“一个人眼中的‘魔法’，在另一个人眼中是工程学。”[NEWLINE]——罗伯特·海因莱因"/&gt;</v>
       </c>
     </row>
-    <row r="71" ht="33" spans="1:3">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>&lt;Replace Tag="LOC_TECH_APPRENTICESHIP_QUOTE_2" Language="zh_Hans_CN" Text="“训练学徒是没有捷径的。我的两大方法是示范和唠叨。”[NEWLINE]——雷蒙·斯尼奇"/&gt;</v>
       </c>
     </row>
-    <row r="76" ht="33" spans="1:3">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>151</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>&lt;Replace Tag="LOC_TECH_STIRRUPS_QUOTE_2" Language="zh_Hans_CN" Text="“在马镫和地面之间，我祈求宽恕，得到了宽恕。”[NEWLINE]——威廉·卡姆登"/&gt;</v>
       </c>
     </row>
-    <row r="78" ht="33" spans="1:3">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>155</v>
       </c>
@@ -4277,7 +4277,7 @@
         <v>&lt;Replace Tag="LOC_TECH_MILITARY_ENGINEERING_QUOTE_1" Language="zh_Hans_CN" Text="“爆破——修筑——作战”[NEWLINE]——美国第十六工兵旅的座右铭"/&gt;</v>
       </c>
     </row>
-    <row r="83" ht="33" spans="1:4">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>166</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>&lt;Replace Tag="LOC_TECH_CASTLES_QUOTE_1" Language="zh_Hans_CN" Text="“前路有石头？我会把它们保存好，然后用来修建我自己的城堡。”[NEWLINE]——内莫·诺克斯"/&gt;</v>
       </c>
     </row>
-    <row r="85" ht="33" spans="1:4">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>&lt;Replace Tag="LOC_TECH_MASS_PRODUCTION_QUOTE_1" Language="zh_Hans_CN" Text="“人们可以选择任何颜色的T型车——只要是黑的就行。”[NEWLINE]——亨利·福特"/&gt;</v>
       </c>
     </row>
-    <row r="88" ht="33" spans="1:4">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>176</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>&lt;Replace Tag="LOC_TECH_MASS_PRODUCTION_QUOTE_2" Language="zh_Hans_CN" Text="“能被贴上标签、包装妥当、大量生产的东西，一定不是真理也不是艺术。”[NEWLINE]——马蒂·鲁宾"/&gt;</v>
       </c>
     </row>
-    <row r="89" ht="33" spans="1:4">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>178</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>&lt;Replace Tag="LOC_TECH_GUNPOWDER_QUOTE_2" Language="zh_Hans_CN" Text="“人是一种军事动物，以火药为荣且乐于列队游行。”[NEWLINE]——菲利普·贝利"/&gt;</v>
       </c>
     </row>
-    <row r="93" ht="33" spans="1:4">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>186</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>&lt;Replace Tag="LOC_TECH_PRINTING_QUOTE_2" Language="zh_Hans_CN" Text="“火药怎么改变了战争，印刷机就怎么改变了思想。”[NEWLINE]——温德尔·菲利浦斯"/&gt;</v>
       </c>
     </row>
-    <row r="95" ht="33" spans="1:4">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>190</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>&lt;Replace Tag="LOC_TECH_ASTRONOMY_QUOTE_2" Language="zh_Hans_CN" Text="“如果你不是个天文学家，天文学就有趣多了。”[NEWLINE]——布赖恩·梅"/&gt;</v>
       </c>
     </row>
-    <row r="99" ht="33" spans="1:3">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>198</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>&lt;Replace Tag="LOC_TECH_METAL_CASTING_QUOTE_1" Language="zh_Hans_CN" Text="“最先，赫菲斯托斯制作了一面强大的巨形盾牌…然后在盾牌上锻造了两座宏伟城市。”[NEWLINE]——荷马"/&gt;</v>
       </c>
     </row>
-    <row r="100" ht="33" spans="1:3">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>200</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SIEGE_TACTICS_QUOTE_2" Language="zh_Hans_CN" Text="“最美好的浪漫都盛开在严密的围城中。”[NEWLINE]——迈尔斯·卡梅隆"/&gt;</v>
       </c>
     </row>
-    <row r="103" ht="33" spans="1:3">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>206</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>&lt;Replace Tag="LOC_TECH_INDUSTRIALIZATION_QUOTE_1" Language="zh_Hans_CN" Text="“我认为工业革命初期，人类犯了一个错误，我们直接跨越到了机械化的东西。人们需要使用双手来感受创造力。”[NEWLINE]——安德鲁·诺顿"/&gt;</v>
       </c>
     </row>
-    <row r="104" ht="33" spans="1:3">
+    <row r="104" spans="1:3">
       <c r="A104" t="s">
         <v>208</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>&lt;Replace Tag="LOC_TECH_INDUSTRIALIZATION_QUOTE_2" Language="zh_Hans_CN" Text="“暴力经济学的关键词是城市化、工业化、集中、效率、数量、速度。”[NEWLINE]——恩斯特·弗里德里希·舒马赫"/&gt;</v>
       </c>
     </row>
-    <row r="105" ht="33" spans="1:3">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>210</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SCIENTIFIC_THEORY_QUOTE_2" Language="zh_Hans_CN" Text="“如果事实和理论不符，那么就修改事实。”[NEWLINE]——阿尔伯特·爱因斯坦"/&gt;</v>
       </c>
     </row>
-    <row r="107" ht="33" spans="1:3">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>&lt;Replace Tag="LOC_TECH_BALLISTICS_QUOTE_1" Language="zh_Hans_CN" Text="“推断什么事情发生了非常重要。但在弹道学算出发生了什么之前，我们不妄自揣测…”[NEWLINE]——约翰·汉森"/&gt;</v>
       </c>
     </row>
-    <row r="108" ht="33" spans="1:3">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>216</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>&lt;Replace Tag="LOC_TECH_MILITARY_SCIENCE_QUOTE_1" Language="zh_Hans_CN" Text="“不管战略看起来多漂亮，都得偶尔看看结果如何。”[NEWLINE]——温斯顿·丘吉尔"/&gt;</v>
       </c>
     </row>
-    <row r="110" ht="33" spans="1:3">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>220</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>&lt;Replace Tag="LOC_TECH_MILITARY_SCIENCE_QUOTE_2" Language="zh_Hans_CN" Text="“没人会这么发起战争——确切说，只要还没疯就不会——不先想清楚要通过战争获得什么，以及具体打算如何去做。”[NEWLINE]——卡尔·冯·克劳塞维茨"/&gt;</v>
       </c>
     </row>
-    <row r="111" ht="33" spans="1:3">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>222</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>&lt;Replace Tag="LOC_TECH_STEAM_POWER_QUOTE_2" Language="zh_Hans_CN" Text="“蒸汽机对科学的贡献远远大于科学对蒸汽机的贡献。”[NEWLINE]——劳伦斯· 亨德尔森"/&gt;</v>
       </c>
     </row>
-    <row r="113" ht="33" spans="1:3">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SANITATION_QUOTE_1" Language="zh_Hans_CN" Text="“过去200年里，在挽救生命与改善健康状况方面，没有任何一项创新可以与抽水马桶的发明引发的卫生革命所产生的意义相提并论。”[NEWLINE]——西尔维娅·伯韦尔"/&gt;</v>
       </c>
     </row>
-    <row r="114" ht="33" spans="1:3">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>228</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>&lt;Replace Tag="LOC_TECH_ECONOMICS_QUOTE_1" Language="zh_Hans_CN" Text="“经济学这门学科不太尊重个人的愿望。”[NEWLINE]——尼基塔·赫鲁晓夫"/&gt;</v>
       </c>
     </row>
-    <row r="116" ht="33" spans="1:3">
+    <row r="116" spans="1:3">
       <c r="A116" t="s">
         <v>232</v>
       </c>
@@ -4697,7 +4697,7 @@
         <v>&lt;Replace Tag="LOC_TECH_RIFLING_QUOTE_1" Language="zh_Hans_CN" Text="“步枪枪机胜于雄辩。”[NEWLINE]——克莱格·罗伯茨"/&gt;</v>
       </c>
     </row>
-    <row r="118" ht="33" spans="1:3">
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
         <v>236</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>&lt;Replace Tag="LOC_TECH_RIFLING_QUOTE_2" Language="zh_Hans_CN" Text="“永远不要批评一位步枪手，除非你穿着他的鞋走一英里。这样，他就会光着脚，而你在他射程以外。”[NEWLINE]——第二标靶公司"/&gt;</v>
       </c>
     </row>
-    <row r="119" ht="33" spans="1:3">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>238</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>&lt;Replace Tag="LOC_TECH_FLIGHT_QUOTE_1" Language="zh_Hans_CN" Text="“一旦尝过飞行的滋味，即便你行走在地面也会仰望天空。因为你曾去过那里，并且渴望回到那里。”[NEWLINE]——列奥纳多·达·芬奇"/&gt;</v>
       </c>
     </row>
-    <row r="120" ht="33" spans="1:3">
+    <row r="120" spans="1:3">
       <c r="A120" t="s">
         <v>240</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>&lt;Replace Tag="LOC_TECH_FLIGHT_QUOTE_2" Language="zh_Hans_CN" Text="“如果着陆后你能走得出机舱，那这个着陆还不错；如果第二天你还能继续用这架飞机，那这个着陆简直棒呆啦。”[NEWLINE]——查克·叶格"/&gt;</v>
       </c>
     </row>
-    <row r="121" ht="33" spans="1:3">
+    <row r="121" spans="1:3">
       <c r="A121" t="s">
         <v>242</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>&lt;Replace Tag="LOC_TECH_REPLACEABLE_PARTS_QUOTE_1" Language="zh_Hans_CN" Text="“要让一台机器运转平稳不出岔子，它的部件必须符合标准，以便替换。”[NEWLINE]——查尔斯·艾森斯坦"/&gt;</v>
       </c>
     </row>
-    <row r="122" ht="33" spans="1:3">
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
         <v>244</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>&lt;Replace Tag="LOC_TECH_CHEMISTRY_QUOTE_1" Language="zh_Hans_CN" Text="“化学是物理学的肮脏部分。”[NEWLINE]——彼得·瑞斯"/&gt;</v>
       </c>
     </row>
-    <row r="130" ht="33" spans="1:3">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>260</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>&lt;Replace Tag="LOC_TECH_CHEMISTRY_QUOTE_2" Language="zh_Hans_CN" Text="“化学家通常说话不结巴。如果结巴的话会非常尴尬，因为他们有时需要说出‘甲基乙基淀粉基苯’之类的玩意儿。”[NEWLINE]——威廉·克鲁克斯爵士"/&gt;</v>
       </c>
     </row>
-    <row r="131" ht="33" spans="1:3">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>262</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>&lt;Replace Tag="LOC_TECH_COMBUSTION_QUOTE_1" Language="zh_Hans_CN" Text="“汽车从我们还是孩子的时候起就没什么进步。归根结底，它仍然只是一台汽油内燃机。”[NEWLINE]——德纳·布鲁奈蒂"/&gt;</v>
       </c>
     </row>
-    <row r="132" ht="33" spans="1:3">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>264</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>&lt;Replace Tag="LOC_TECH_COMBUSTION_QUOTE_2" Language="zh_Hans_CN" Text="“我一直认为用内燃机来替代马匹是人类历史进程中一件很令人沮丧的事。”[NEWLINE]——温斯顿·丘吉尔"/&gt;</v>
       </c>
     </row>
-    <row r="133" ht="33" spans="1:3">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
         <v>266</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>&lt;Replace Tag="LOC_TECH_ADVANCED_FLIGHT_QUOTE_1" Language="zh_Hans_CN" Text="“是，飞机又快又实惠，不过，天啊，一味追求效率，我们得失去多少快乐，牺牲多少休闲时光啊。”[NEWLINE]——金吉·罗杰斯"/&gt;</v>
       </c>
     </row>
-    <row r="134" ht="33" spans="1:3">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>268</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>&lt;Replace Tag="LOC_TECH_ROCKETRY_QUOTE_1" Language="zh_Hans_CN" Text="“火箭科学已经被神化了，使其与它的实际难度并不相称。”[NEWLINE]——约翰·卡马克"/&gt;</v>
       </c>
     </row>
-    <row r="136" ht="33" spans="1:3">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>272</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>&lt;Replace Tag="LOC_TECH_COMBINED_ARMS_QUOTE_2" Language="zh_Hans_CN" Text="“战争中最不可估量的东西是人的意志力。”[NEWLINE]——巴兹尔·亨利·利德尔·哈特"/&gt;</v>
       </c>
     </row>
-    <row r="141" ht="33" spans="1:3">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>282</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>&lt;Replace Tag="LOC_TECH_COMPUTERS_QUOTE_1" Language="zh_Hans_CN" Text="“人都会犯错，但是想真正把事情搞砸你得要一台电脑。” [NEWLINE]——保罗·拉尔夫·埃利希"/&gt;</v>
       </c>
     </row>
-    <row r="144" ht="33" spans="1:3">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
         <v>288</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>&lt;Replace Tag="LOC_TECH_COMPUTERS_QUOTE_2" Language="zh_Hans_CN" Text="“电脑的优点是你让它做什么，它就做什么。坏处是你让它做什么，它就做什么。”[NEWLINE]——泰德·尼尔森"/&gt;</v>
       </c>
     </row>
-    <row r="145" ht="33" spans="1:3">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>290</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>&lt;Replace Tag="LOC_TECH_NUCLEAR_FISSION_QUOTE_2" Language="zh_Hans_CN" Text="“别碰原子能。”[NEWLINE]——埃德加·伊普塞尔·哈伯格"/&gt;</v>
       </c>
     </row>
-    <row r="147" ht="33" spans="1:3">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
         <v>294</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SATELLITES_QUOTE_1" Language="zh_Hans_CN" Text="“卫星无良知。”[NEWLINE]——爱德华·默罗"/&gt;</v>
       </c>
     </row>
-    <row r="152" ht="33" spans="1:3">
+    <row r="152" spans="1:3">
       <c r="A152" t="s">
         <v>304</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SATELLITES_QUOTE_2" Language="zh_Hans_CN" Text="“就在现在，有31颗卫星在满世界飞驰，而它们除了帮你找到去杂货店的路以外，也干不了更好的事了。”[NEWLINE]——埃德·伯内特"/&gt;</v>
       </c>
     </row>
-    <row r="153" ht="33" spans="1:3">
+    <row r="153" spans="1:3">
       <c r="A153" t="s">
         <v>306</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>&lt;Replace Tag="LOC_TECH_LASERS_QUOTE_2" Language="zh_Hans_CN" Text="“我是一个超级激光信徒——我相信它们肯定是未来潮流。”[NEWLINE]——柯特妮·考克斯"/&gt;</v>
       </c>
     </row>
-    <row r="157" ht="33" spans="1:3">
+    <row r="157" spans="1:3">
       <c r="A157" t="s">
         <v>314</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>&lt;Replace Tag="LOC_TECH_COMPOSITES_QUOTE_1" Language="zh_Hans_CN" Text="“所有物质看起来都是由坚实的粒子组成的…在某个智能体的指引下，以不同的方式与最初的造物联系在一起。”[NEWLINE]——艾萨克·牛顿"/&gt;</v>
       </c>
     </row>
-    <row r="158" ht="33" spans="1:3">
+    <row r="158" spans="1:3">
       <c r="A158" t="s">
         <v>316</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>&lt;Replace Tag="LOC_TECH_COMPOSITES_QUOTE_2" Language="zh_Hans_CN" Text="“很明显，当科学正努力让天堂降临人间时，一些人却在使用它的建材来建造地狱。”[NEWLINE]——赫伯特·胡佛"/&gt;</v>
       </c>
     </row>
-    <row r="159" ht="33" spans="1:3">
+    <row r="159" spans="1:3">
       <c r="A159" t="s">
         <v>318</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>&lt;Replace Tag="LOC_TECH_STEALTH_TECHNOLOGY_QUOTE_1" Language="zh_Hans_CN" Text="“我想说的是隐形是一种有趣的能力，你可以穿过世界看看它到底是什么样子，而没人能看到你。”[NEWLINE]——凯文·贝肯"/&gt;</v>
       </c>
     </row>
-    <row r="160" ht="33" spans="1:3">
+    <row r="160" spans="1:3">
       <c r="A160" t="s">
         <v>320</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>&lt;Replace Tag="LOC_TECH_STEALTH_TECHNOLOGY_QUOTE_2" Language="zh_Hans_CN" Text="“在艺术和梦想中，你应当恣意放纵；在生活中，你应当保持平衡，低调到隐形。”[NEWLINE]——帕蒂·史密斯"/&gt;</v>
       </c>
     </row>
-    <row r="161" ht="33" spans="1:3">
+    <row r="161" spans="1:3">
       <c r="A161" t="s">
         <v>322</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>&lt;Replace Tag="LOC_TECH_NANOTECHNOLOGY_QUOTE_1" Language="zh_Hans_CN" Text="“如果科技是变革的引擎，那么纳米技术是人类未来的油料。”[NEWLINE]——娜塔莎·维塔莫尔"/&gt;</v>
       </c>
     </row>
-    <row r="164" ht="33" spans="1:3">
+    <row r="164" spans="1:3">
       <c r="A164" t="s">
         <v>328</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>&lt;Replace Tag="LOC_TECH_FUTURE_TECH_QUOTE_2" Language="zh_Hans_CN" Text="“虽然未来似乎很遥远，但其实已经开始了。”[NEWLINE]——马蒂·斯特帕尼克"/&gt;</v>
       </c>
     </row>
-    <row r="167" ht="33" spans="1:3">
+    <row r="167" spans="1:3">
       <c r="A167" t="s">
         <v>334</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>&lt;Replace Tag="LOC_TECH_NUCLEAR_FUSION_QUOTE_1" Language="zh_Hans_CN" Text="“我非常支持掌控核聚变能量——在1.5亿千米外掌控。我们太阳的聚变干得非常非常不错，而且还不收钱。地球这边的反应堆里…就没那么好了。”[NEWLINE]——乔·罗姆"/&gt;</v>
       </c>
     </row>
-    <row r="168" ht="33" spans="1:3">
+    <row r="168" spans="1:3">
       <c r="A168" t="s">
         <v>336</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>&lt;Replace Tag="LOC_TECH_NUCLEAR_FUSION_QUOTE_2" Language="zh_Hans_CN" Text="“当我们在夜晚仰望星星时，我们看到的一切闪亮都来自遥远的核聚变。”[NEWLINE]——卡尔·萨根"/&gt;</v>
       </c>
     </row>
-    <row r="169" ht="33" spans="1:3">
+    <row r="169" spans="1:3">
       <c r="A169" t="s">
         <v>338</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>&lt;Replace Tag="LOC_TECH_BUTTRESS_QUOTE_1" Language="zh_Hans_CN" Text="“真正的建筑师应该像画匠一样少呆在城市里。要让他登上山峰，学习大自然对何为扶壁、何为穹顶的理解。”[NEWLINE]——约翰·罗斯金"/&gt;</v>
       </c>
     </row>
-    <row r="170" ht="33" spans="1:3">
+    <row r="170" spans="1:3">
       <c r="A170" t="s">
         <v>340</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>&lt;Replace Tag="LOC_TECH_BUTTRESS_QUOTE_2" Language="zh_Hans_CN" Text="“得胜的，我要使他在我神的殿中作柱子，他必不再从那里出去。”[NEWLINE]——《启示录》3:12"/&gt;</v>
       </c>
     </row>
-    <row r="171" ht="33" spans="1:3">
+    <row r="171" spans="1:3">
       <c r="A171" t="s">
         <v>342</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>&lt;Replace Tag="LOC_TECH_REFINING_QUOTE_1" Language="zh_Hans_CN" Text="“所谓工程，就是一门将大自然中绝佳的能量源用于惠世济民的艺术。”[NEWLINE]——托马斯·特雷戈德"/&gt;</v>
       </c>
     </row>
-    <row r="172" ht="33" spans="1:3">
+    <row r="172" spans="1:3">
       <c r="A172" t="s">
         <v>344</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SEASTEADS_QUOTE_1" Language="zh_Hans_CN" Text="“我务须再度潜入那无底深海，如流浪吉卜赛人一般生活；在那里，疾风如利刃般刺骨，而我如海鸥般恣意翱翔，如鲸鱼般纵情遨游。”[NEWLINE]——约翰·麦斯菲尔"/&gt;</v>
       </c>
     </row>
-    <row r="173" ht="33" spans="1:3">
+    <row r="173" spans="1:3">
       <c r="A173" t="s">
         <v>346</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>&lt;Replace Tag="LOC_TECH_SEASTEADS_QUOTE_2" Language="zh_Hans_CN" Text="“于是你扬帆出航，前往那乌云密布之处；船桨划破水面，所发之声空泛而无助；随后数月，务须傲然凝视前路。”[NEWLINE]——鲁德亚德·吉卜林"/&gt;</v>
       </c>
     </row>
-    <row r="174" ht="33" spans="1:3">
+    <row r="174" spans="1:3">
       <c r="A174" t="s">
         <v>348</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>&lt;Replace Tag="LOC_TECH_ADVANCED_POWER_CELLS_QUOTE_1" Language="zh_Hans_CN" Text="“曲则全，枉则直，洼则盈，敝则新。”[NEWLINE]——老子《道德经》"/&gt;</v>
       </c>
     </row>
-    <row r="176" ht="49.5" spans="1:3">
+    <row r="176" spans="1:3">
       <c r="A176" t="s">
         <v>352</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>&lt;Replace Tag="LOC_TECH_CYBERNETICS_QUOTE_1" Language="zh_Hans_CN" Text="“如果来生有劳作，那你须替我受其劳。一旦我有所召唤，你须即刻回应。在此劳作之时需谨言慎行。耕我之田，将水和沙运往东西四方。一旦我有所召唤，你须即刻回应。”[NEWLINE]——埃及巫沙布提俑铭文"/&gt;</v>
       </c>
     </row>
-    <row r="177" ht="33" spans="1:4">
+    <row r="177" spans="1:4">
       <c r="A177" t="s">
         <v>354</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>&lt;Replace Tag="LOC_TECH_PREDICTIVE_SYSTEMS_QUOTE_1" Language="zh_Hans_CN" Text="“敌所备者多，则吾所与战者，寡矣。”[NEWLINE]——孙子"/&gt;</v>
       </c>
     </row>
-    <row r="179" ht="49.5" spans="1:4">
+    <row r="179" spans="1:4">
       <c r="A179" t="s">
         <v>358</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>&lt;Replace Tag="LOC_TECH_OFFWORLD_MISSION_QUOTE_1" Language="zh_Hans_CN" Text="“不，我的朋友，我们没有回到地球，我们也没有坠入墨西哥湾。相反，我们正冲向太空，亲眼见证那些在夜空中闪耀的明星，还有地球和我们之间堆积的重重黑幕！”[NEWLINE]——儒勒·凡尔纳"/&gt;</v>
       </c>
     </row>
-    <row r="180" ht="33" spans="1:4">
+    <row r="180" spans="1:4">
       <c r="A180" t="s">
         <v>360</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CODE_OF_LAWS_QUOTE_1" Language="zh_Hans_CN" Text="“制定法律的不是智慧，而是权威。”[NEWLINE]——托马斯·霍布斯"/&gt;</v>
       </c>
     </row>
-    <row r="182" ht="33" spans="1:4">
+    <row r="182" spans="1:4">
       <c r="A182" t="s">
         <v>364</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CRAFTSMANSHIP_QUOTE_1" Language="zh_Hans_CN" Text="“没有技艺，灵感不过是风中摇曳的芦苇。”[NEWLINE]——约翰内斯·勃拉姆斯"/&gt;</v>
       </c>
     </row>
-    <row r="184" ht="33" spans="1:4">
+    <row r="184" spans="1:4">
       <c r="A184" t="s">
         <v>368</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MILITARY_TRADITION_QUOTE_1" Language="zh_Hans_CN" Text="“所谓勇敢，就是只有你自己知道自己在恐惧。”[NEWLINE]——大卫·哈克沃斯上校"/&gt;</v>
       </c>
     </row>
-    <row r="188" ht="33" spans="1:4">
+    <row r="188" spans="1:4">
       <c r="A188" t="s">
         <v>377</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_EARLY_EMPIRE_QUOTE_1" Language="zh_Hans_CN" Text="“回顾过去，遍观帝国兴衰，你便也能预见未来。”[NEWLINE]——马可·奥勒留"/&gt;</v>
       </c>
     </row>
-    <row r="192" ht="33" spans="1:4">
+    <row r="192" spans="1:4">
       <c r="A192" t="s">
         <v>385</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_EARLY_EMPIRE_QUOTE_2" Language="zh_Hans_CN" Text="“空调这样的奢侈品摧毁了罗马帝国。有了空调，他们就关上了窗户；他们就听不见蛮族来了。”[NEWLINE]——加里森·凯勒"/&gt;</v>
       </c>
     </row>
-    <row r="193" ht="33" spans="1:3">
+    <row r="193" spans="1:3">
       <c r="A193" t="s">
         <v>387</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MYSTICISM_QUOTE_1" Language="zh_Hans_CN" Text="“神秘主义就是把意外和个例的巧合错当成了普遍的征兆。”[NEWLINE]——拉尔夫·瓦尔多·爱默生"/&gt;</v>
       </c>
     </row>
-    <row r="194" ht="33" spans="1:3">
+    <row r="194" spans="1:3">
       <c r="A194" t="s">
         <v>389</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_GAMES_RECREATION_QUOTE_2" Language="zh_Hans_CN" Text="“没有时间娱乐的人，迟早得有时间生病。” [NEWLINE]——约翰·沃纳梅克"/&gt;</v>
       </c>
     </row>
-    <row r="197" ht="33" spans="1:3">
+    <row r="197" spans="1:3">
       <c r="A197" t="s">
         <v>395</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_RECORDED_HISTORY_QUOTE_2" Language="zh_Hans_CN" Text="“历史就是人们一致决定认可的版本的往事记录。”[NEWLINE]——拿破仑·波拿巴"/&gt;</v>
       </c>
     </row>
-    <row r="207" ht="33" spans="1:3">
+    <row r="207" spans="1:3">
       <c r="A207" t="s">
         <v>415</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_NAVAL_TRADITION_QUOTE_1" Language="zh_Hans_CN" Text="“强大的海军不是挑起战争的祸端，而是最可靠的和平卫士。”[NEWLINE]——西奥多·罗斯福"/&gt;</v>
       </c>
     </row>
-    <row r="210" ht="33" spans="1:3">
+    <row r="210" spans="1:3">
       <c r="A210" t="s">
         <v>421</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_NAVAL_TRADITION_QUOTE_2" Language="zh_Hans_CN" Text="“海军里既有传统，也有未来——在这两方面，我们都充满自豪和信心。” [NEWLINE]——阿利·伯克"/&gt;</v>
       </c>
     </row>
-    <row r="211" ht="33" spans="1:3">
+    <row r="211" spans="1:3">
       <c r="A211" t="s">
         <v>423</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_FEUDALISM_QUOTE_1" Language="zh_Hans_CN" Text="“在民主政体里，你有投票的地位。在封建国家里，你有地位才有票投。”[NEWLINE]——莫根斯·加尔贝格"/&gt;</v>
       </c>
     </row>
-    <row r="212" ht="33" spans="1:3">
+    <row r="212" spans="1:3">
       <c r="A212" t="s">
         <v>425</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_FEUDALISM_QUOTE_2" Language="zh_Hans_CN" Text="“随着封建主义走向高峰，铁盔甲也随之改进，直到最后出现了穿得像犰狳一样的战士。”[NEWLINE]——约翰·博伊尔·奥莱利"/&gt;</v>
       </c>
     </row>
-    <row r="213" ht="33" spans="1:3">
+    <row r="213" spans="1:3">
       <c r="A213" t="s">
         <v>427</v>
       </c>
@@ -5864,7 +5864,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CIVIL_SERVICE_QUOTE_2" Language="zh_Hans_CN" Text="“纳税人——就是为政府工作但不需要参加公务员考试的人。”[NEWLINE]——罗纳德·里根"/&gt;</v>
       </c>
     </row>
-    <row r="215" ht="33" spans="1:3">
+    <row r="215" spans="1:3">
       <c r="A215" t="s">
         <v>431</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MERCENARIES_QUOTE_1" Language="zh_Hans_CN" Text="“人在和平时期，受到雇佣兵掠夺；战争时期，受到敌人掠夺。”[NEWLINE]——尼可罗·马基亚维利"/&gt;</v>
       </c>
     </row>
-    <row r="216" ht="33" spans="1:3">
+    <row r="216" spans="1:3">
       <c r="A216" t="s">
         <v>433</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MEDIEVAL_FAIRES_QUOTE_1" Language="zh_Hans_CN" Text="“发光的不一定都是金子；你常常会听到大家这样说。”[NEWLINE]——威廉·莎士比亚"/&gt;</v>
       </c>
     </row>
-    <row r="218" ht="33" spans="1:3">
+    <row r="218" spans="1:3">
       <c r="A218" t="s">
         <v>437</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MEDIEVAL_FAIRES_QUOTE_2" Language="zh_Hans_CN" Text="“有些非常诚实的人，只有骗了商人一道，他们才会觉得自己捡了便宜。”[NEWLINE]——阿纳托尔·法郎士"/&gt;</v>
       </c>
     </row>
-    <row r="219" ht="33" spans="1:3">
+    <row r="219" spans="1:3">
       <c r="A219" t="s">
         <v>439</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_GUILDS_QUOTE_1" Language="zh_Hans_CN" Text="“每个人都应该让他的儿子多学习有用的手艺或专业知识，这样在世道改变的时候…他们才能有靠来吃饭的本事。”[NEWLINE]——费尼尔司·泰勒·巴纳姆"/&gt;</v>
       </c>
     </row>
-    <row r="220" ht="33" spans="1:3">
+    <row r="220" spans="1:3">
       <c r="A220" t="s">
         <v>441</v>
       </c>
@@ -5936,7 +5936,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_GUILDS_QUOTE_2" Language="zh_Hans_CN" Text="“你怎么能莫名其妙地逮捕盗贼公会？我是说，那我们就整天不得闲了！”[NEWLINE]——特里·普拉切特"/&gt;</v>
       </c>
     </row>
-    <row r="221" ht="33" spans="1:3">
+    <row r="221" spans="1:3">
       <c r="A221" t="s">
         <v>443</v>
       </c>
@@ -5948,7 +5948,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_DIVINE_RIGHT_QUOTE_1" Language="zh_Hans_CN" Text="“朕以此神性公理推断出关于王权的如下结论：质疑上帝所为即渎神…因此质疑国王所为是为叛乱。”[NEWLINE]——詹姆斯一世"/&gt;</v>
       </c>
     </row>
-    <row r="222" ht="33" spans="1:3">
+    <row r="222" spans="1:3">
       <c r="A222" t="s">
         <v>445</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_DIVINE_RIGHT_QUOTE_2" Language="zh_Hans_CN" Text="“听我说，池塘里面有奇怪女人给人发剑，这不是建立政权的依据…你不能因为有个水里的烧鸡给你把剑就觉得自己大权在握了吧！”[NEWLINE]——巨蟒剧团"/&gt;</v>
       </c>
     </row>
-    <row r="223" ht="33" spans="1:3">
+    <row r="223" spans="1:3">
       <c r="A223" t="s">
         <v>447</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_EXPLORATION_QUOTE_1" Language="zh_Hans_CN" Text="“我们停止探索的时候就是我们打算从此生活在停滞不前的世界的时候。这样的世界好奇心全无，梦想空荡荡。”[NEWLINE]——奈尔·德葛拉司·泰森"/&gt;</v>
       </c>
     </row>
-    <row r="224" ht="33" spans="1:3">
+    <row r="224" spans="1:3">
       <c r="A224" t="s">
         <v>449</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_EXPLORATION_QUOTE_2" Language="zh_Hans_CN" Text="“我们不应停止探索，在所有探索的尽头，我们会回到起点，重新认识这个地方。”[NEWLINE]——托马斯·斯特尔那斯·艾略特"/&gt;</v>
       </c>
     </row>
-    <row r="225" ht="33" spans="1:3">
+    <row r="225" spans="1:3">
       <c r="A225" t="s">
         <v>451</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_HUMANISM_QUOTE_1" Language="zh_Hans_CN" Text="“人文主义的四大特点是：好奇心、自由思想、相信好品味、相信人类。”[NEWLINE]——爱德华·摩根·福斯特"/&gt;</v>
       </c>
     </row>
-    <row r="226" ht="33" spans="1:3">
+    <row r="226" spans="1:3">
       <c r="A226" t="s">
         <v>453</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_HUMANISM_QUOTE_2" Language="zh_Hans_CN" Text="“不可对人性失去信心。人性就像大海；即便海洋中会有几滴水是脏的，大海也不会变脏。”[NEWLINE]——圣雄甘地"/&gt;</v>
       </c>
     </row>
-    <row r="227" ht="33" spans="1:3">
+    <row r="227" spans="1:3">
       <c r="A227" t="s">
         <v>455</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_DIPLOMATIC_SERVICE_QUOTE_1" Language="zh_Hans_CN" Text="“外交领域有两种问题：小问题和大问题。小问题会自己消失，大问题你无可奈何。”[NEWLINE]——帕特里克·麦基尼斯"/&gt;</v>
       </c>
     </row>
-    <row r="228" ht="33" spans="1:3">
+    <row r="228" spans="1:3">
       <c r="A228" t="s">
         <v>457</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_DIPLOMATIC_SERVICE_QUOTE_2" Language="zh_Hans_CN" Text="“外交官就是总是记得女人的生日而永远不记得她的年龄的人。”[NEWLINE]——罗伯特·弗罗斯特"/&gt;</v>
       </c>
     </row>
-    <row r="229" ht="33" spans="1:3">
+    <row r="229" spans="1:3">
       <c r="A229" t="s">
         <v>459</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MERCANTILISM_QUOTE_1" Language="zh_Hans_CN" Text="“但是在市场经济条件下，个人可能会逃脱国家的管束。”[NEWLINE]——彼得·伯格"/&gt;</v>
       </c>
     </row>
-    <row r="232" ht="33" spans="1:3">
+    <row r="232" spans="1:3">
       <c r="A232" t="s">
         <v>465</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MERCANTILISM_QUOTE_2" Language="zh_Hans_CN" Text="“在见识了非市场经济后，我突然更明白了我喜欢市场经济的哪些方面。”[NEWLINE]——艾瑟·戴森"/&gt;</v>
       </c>
     </row>
-    <row r="233" ht="33" spans="1:3">
+    <row r="233" spans="1:3">
       <c r="A233" t="s">
         <v>467</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_THE_ENLIGHTENMENT_QUOTE_1" Language="zh_Hans_CN" Text="“新观念总是遭到怀疑和反对，没有别的原因，只是因为人们习惯于旧的东西。”[NEWLINE]—— 约翰·洛克"/&gt;</v>
       </c>
     </row>
-    <row r="234" ht="33" spans="1:3">
+    <row r="234" spans="1:3">
       <c r="A234" t="s">
         <v>469</v>
       </c>
@@ -6104,7 +6104,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_THE_ENLIGHTENMENT_QUOTE_2" Language="zh_Hans_CN" Text="“任何反自然的东西都是反理性的，任何反理性的东西都是荒诞可笑的。”[NEWLINE]——巴鲁赫·斯宾诺莎"/&gt;</v>
       </c>
     </row>
-    <row r="235" ht="33" spans="1:3">
+    <row r="235" spans="1:3">
       <c r="A235" t="s">
         <v>471</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_COLONIALISM_QUOTE_1" Language="zh_Hans_CN" Text="“记住：政治、殖民主义、帝国主义和战争也都源于人类的大脑。”[NEWLINE]——维兰亚努·拉玛钱德朗"/&gt;</v>
       </c>
     </row>
-    <row r="236" ht="33" spans="1:3">
+    <row r="236" spans="1:3">
       <c r="A236" t="s">
         <v>473</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CIVIL_ENGINEERING_QUOTE_1" Language="zh_Hans_CN" Text="“改造使弯路变得笔直；但未经改造的弯路才是成就天才之路。”[NEWLINE]——威廉·布雷克"/&gt;</v>
       </c>
     </row>
-    <row r="238" ht="33" spans="1:3">
+    <row r="238" spans="1:3">
       <c r="A238" t="s">
         <v>477</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_NATIONALISM_QUOTE_1" Language="zh_Hans_CN" Text="“民族主义促使国家产生，而不是国家产生了民族主义。”[NEWLINE]——欧内斯特·盖尔纳"/&gt;</v>
       </c>
     </row>
-    <row r="240" ht="33" spans="1:3">
+    <row r="240" spans="1:3">
       <c r="A240" t="s">
         <v>481</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_NATIONALISM_QUOTE_2" Language="zh_Hans_CN" Text="“人类在部落主义和民族主义中表现出的天性驱动了人类进化的机器。”[NEWLINE]——阿瑟·基思"/&gt;</v>
       </c>
     </row>
-    <row r="241" ht="33" spans="1:3">
+    <row r="241" spans="1:3">
       <c r="A241" t="s">
         <v>483</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_OPERA_BALLET_QUOTE_2" Language="zh_Hans_CN" Text="“它（芭蕾）表现出一种精致的力量和某种不屈不挠的准确。”[NEWLINE]——艾茵·兰德"/&gt;</v>
       </c>
     </row>
-    <row r="243" ht="33" spans="1:3">
+    <row r="243" spans="1:3">
       <c r="A243" t="s">
         <v>487</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_NATURAL_HISTORY_QUOTE_1" Language="zh_Hans_CN" Text="“如果创世纪的时候我在场，我会提出一些改善宇宙秩序的建议。”[NEWLINE]——纳尔逊·艾格林"/&gt;</v>
       </c>
     </row>
-    <row r="244" ht="33" spans="1:3">
+    <row r="244" spans="1:3">
       <c r="A244" t="s">
         <v>489</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_URBANIZATION_QUOTE_2" Language="zh_Hans_CN" Text="“我喜欢城市的一点是里面的一切都是加大号的，不论美丑。”[NEWLINE]——约瑟夫·布罗茨基"/&gt;</v>
       </c>
     </row>
-    <row r="249" ht="33" spans="1:3">
+    <row r="249" spans="1:3">
       <c r="A249" t="s">
         <v>499</v>
       </c>
@@ -6284,7 +6284,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CAPITALISM_QUOTE_1" Language="zh_Hans_CN" Text="“资本主义的固有罪恶是有福不同享；社会主义的天然美德是有难要同当。” [NEWLINE]——温斯顿·丘吉尔"/&gt;</v>
       </c>
     </row>
-    <row r="250" ht="33" spans="1:3">
+    <row r="250" spans="1:3">
       <c r="A250" t="s">
         <v>501</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CAPITALISM_QUOTE_2" Language="zh_Hans_CN" Text="“一定要试着多蹭蹭财富，只要蹭得够久，没准能蹭下来一点给你。”[NEWLINE]——达蒙·鲁尼恩"/&gt;</v>
       </c>
     </row>
-    <row r="251" ht="33" spans="1:3">
+    <row r="251" spans="1:3">
       <c r="A251" t="s">
         <v>503</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CONSERVATION_QUOTE_1" Language="zh_Hans_CN" Text="“水和空气，这两样生命所依赖的东西，如今已变成了全球的垃圾桶。”[NEWLINE]——雅克·伊夫·库斯托"/&gt;</v>
       </c>
     </row>
-    <row r="252" ht="33" spans="1:3">
+    <row r="252" spans="1:3">
       <c r="A252" t="s">
         <v>505</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MASS_MEDIA_QUOTE_2" Language="zh_Hans_CN" Text="“不看报纸，不知世事。看了报纸，错知世事。”[NEWLINE]——马克·吐温"/&gt;</v>
       </c>
     </row>
-    <row r="255" ht="33" spans="1:3">
+    <row r="255" spans="1:3">
       <c r="A255" t="s">
         <v>511</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MOBILIZATION_QUOTE_1" Language="zh_Hans_CN" Text="“当他们为战争做准备时，那些靠武力统治的人会连篇累牍地大谈和平，直到完成整个动员过程。”[NEWLINE]——斯蒂芬·茨威格"/&gt;</v>
       </c>
     </row>
-    <row r="256" ht="33" spans="1:3">
+    <row r="256" spans="1:3">
       <c r="A256" t="s">
         <v>513</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_MOBILIZATION_QUOTE_2" Language="zh_Hans_CN" Text="“为了号召人民，政府需要敌人…如果没有真正的敌人，他们会造一个，以此让大家动员起来。”[NEWLINE]——一行禅师"/&gt;</v>
       </c>
     </row>
-    <row r="257" ht="33" spans="1:3">
+    <row r="257" spans="1:3">
       <c r="A257" t="s">
         <v>515</v>
       </c>
@@ -6380,7 +6380,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_NUCLEAR_PROGRAM_QUOTE_1" Language="zh_Hans_CN" Text="“原子能的释放改变了除人类思考模式之外的一切…解决这个问题的方法在于人心。早知如此，我就该当个钟表匠。”[NEWLINE]——阿尔伯特·爱因斯坦"/&gt;</v>
       </c>
     </row>
-    <row r="258" ht="33" spans="1:3">
+    <row r="258" spans="1:3">
       <c r="A258" t="s">
         <v>517</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_IDEOLOGY_QUOTE_1" Language="zh_Hans_CN" Text="“已有证明，再没人性的体系，也不能离开意识形态而继续存在。”[NEWLINE]——乔·斯洛沃"/&gt;</v>
       </c>
     </row>
-    <row r="260" ht="33" spans="1:3">
+    <row r="260" spans="1:3">
       <c r="A260" t="s">
         <v>521</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_IDEOLOGY_QUOTE_2" Language="zh_Hans_CN" Text="“慢慢地，思想催生出意识形态，催生出政策，最后催生出行动。”[NEWLINE]——南丹·尼勒卡尼"/&gt;</v>
       </c>
     </row>
-    <row r="261" ht="33" spans="1:3">
+    <row r="261" spans="1:3">
       <c r="A261" t="s">
         <v>523</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_SUFFRAGE_QUOTE_1" Language="zh_Hans_CN" Text="“为什么女人就要被区别对待？妇女选举权运动将会成功，不会被这些可怜的散兵游勇的反对影响。”[NEWLINE]——维多利亚·伍德胡尔"/&gt;</v>
       </c>
     </row>
-    <row r="262" ht="33" spans="1:3">
+    <row r="262" spans="1:3">
       <c r="A262" t="s">
         <v>525</v>
       </c>
@@ -6440,7 +6440,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_SUFFRAGE_QUOTE_2" Language="zh_Hans_CN" Text="“男人有男人的权利，不能拿更多；女人有女人的权利，不能少一点！” [NEWLINE]——苏珊·安东尼"/&gt;</v>
       </c>
     </row>
-    <row r="263" ht="33" spans="1:3">
+    <row r="263" spans="1:3">
       <c r="A263" t="s">
         <v>527</v>
       </c>
@@ -6464,7 +6464,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_TOTALITARIANISM_QUOTE_2" Language="zh_Hans_CN" Text="“任何意识形态的终极都是极权主义。”[NEWLINE]——汤姆·罗宾斯"/&gt;</v>
       </c>
     </row>
-    <row r="265" ht="33" spans="1:3">
+    <row r="265" spans="1:3">
       <c r="A265" t="s">
         <v>531</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CLASS_STRUGGLE_QUOTE_2" Language="zh_Hans_CN" Text="“阶级斗争必然要导致无产阶级专政。”[NEWLINE]——卡尔·马克思"/&gt;</v>
       </c>
     </row>
-    <row r="267" ht="33" spans="1:3">
+    <row r="267" spans="1:3">
       <c r="A267" t="s">
         <v>535</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_PROFESSIONAL_SPORTS_QUOTE_2" Language="zh_Hans_CN" Text="“竞技体育不能塑造人的性格。但能体现人的性格。”[NEWLINE]——海伍德·布朗"/&gt;</v>
       </c>
     </row>
-    <row r="271" ht="33" spans="1:3">
+    <row r="271" spans="1:3">
       <c r="A271" t="s">
         <v>543</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CULTURAL_HERITAGE_QUOTE_1" Language="zh_Hans_CN" Text="“一个对自己历史、起源和文化不了解的民族，就好比没有根的大树。”[NEWLINE]——马库斯·加维"/&gt;</v>
       </c>
     </row>
-    <row r="272" ht="33" spans="1:3">
+    <row r="272" spans="1:3">
       <c r="A272" t="s">
         <v>545</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CULTURAL_HERITAGE_QUOTE_2" Language="zh_Hans_CN" Text="“文化遗产不是偶然撞见的。它们就在那里，等着你去探寻，去分享。”[NEWLINE]——罗比·罗伯森"/&gt;</v>
       </c>
     </row>
-    <row r="273" ht="33" spans="1:3">
+    <row r="273" spans="1:3">
       <c r="A273" t="s">
         <v>547</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_RAPID_DEPLOYMENT_QUOTE_2" Language="zh_Hans_CN" Text="“别管什么机动，给我朝他们直冲。”[NEWLINE]——霍雷肖·纳尔逊"/&gt;</v>
       </c>
     </row>
-    <row r="275" ht="33" spans="1:3">
+    <row r="275" spans="1:3">
       <c r="A275" t="s">
         <v>551</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_SPACE_RACE_QUOTE_1" Language="zh_Hans_CN" Text="“我们选择在这个十年飞向月球，并做些其他的事，不是因为它们容易，而是因为它们很难。”[NEWLINE]——约翰·菲茨杰拉德·肯尼迪"/&gt;</v>
       </c>
     </row>
-    <row r="276" ht="33" spans="1:3">
+    <row r="276" spans="1:3">
       <c r="A276" t="s">
         <v>553</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_GLOBALIZATION_QUOTE_1" Language="zh_Hans_CN" Text="“有人说，反对全球化就像反对万有引力定律。”[NEWLINE]——科菲·安南"/&gt;</v>
       </c>
     </row>
-    <row r="278" ht="33" spans="1:3">
+    <row r="278" spans="1:3">
       <c r="A278" t="s">
         <v>557</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_FUTURE_CIVIC_QUOTE_2" Language="zh_Hans_CN" Text="“我从不思考未来。因为它来得也够快的。”[NEWLINE]——阿尔伯特·爱因斯坦"/&gt;</v>
       </c>
     </row>
-    <row r="283" ht="33" spans="1:3">
+    <row r="283" spans="1:3">
       <c r="A283" t="s">
         <v>567</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_DIGITAL_DEMOCRACY_QUOTE_1" Language="zh_Hans_CN" Text="“在断定谷有许多许多的人， 因为耶和华的日子临近断定谷了。”[NEWLINE]——《约珥书》3:14"/&gt;</v>
       </c>
     </row>
-    <row r="284" ht="49.5" spans="1:3">
+    <row r="284" spans="1:3">
       <c r="A284" t="s">
         <v>569</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_SYNTHETIC_TECHNOCRACY_QUOTE_1" Language="zh_Hans_CN" Text="“我们发现，机械天才、感知敏锐之人和智力拔群之人皆毫无犹豫地断言自动机是纯粹的机器，其行为不受人工操控。也正是因此，它无可比拟地成为了人类最伟大的发明。”[NEWLINE]——埃德加·艾伦·坡"/&gt;</v>
       </c>
     </row>
-    <row r="285" ht="33" spans="1:3">
+    <row r="285" spans="1:3">
       <c r="A285" t="s">
         <v>571</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_CORPORATE_LIBERTARIANISM_QUOTE_1" Language="zh_Hans_CN" Text="“对于他自己，对于他的身体和心智，个人是最高主权者。”[NEWLINE]——约翰·斯图尔特·密尔"/&gt;</v>
       </c>
     </row>
-    <row r="286" ht="33" spans="1:3">
+    <row r="286" spans="1:3">
       <c r="A286" t="s">
         <v>573</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_EXODUS_IMPERATIVE_QUOTE_1" Language="zh_Hans_CN" Text="“我最亲爱的孩子啊，这又是个很久很久以前的故事啦。”[NEWLINE]——鲁德亚德·吉卜林"/&gt;</v>
       </c>
     </row>
-    <row r="288" ht="49.5" spans="1:3">
+    <row r="288" spans="1:3">
       <c r="A288" t="s">
         <v>577</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_INFORMATION_WARFARE_QUOTE_2" Language="zh_Hans_CN" Text="“吾所与战之地不可知，不可知，则敌所备者多。”[NEWLINE]——孙子"/&gt;</v>
       </c>
     </row>
-    <row r="291" ht="33" spans="1:3">
+    <row r="291" spans="1:3">
       <c r="A291" t="s">
         <v>583</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_GLOBAL_WARMING_MITIGATION_QUOTE_1" Language="zh_Hans_CN" Text="“将这恶人用精金所制的镣铐，[NEWLINE]牢牢锁在尖锐的岩石上。”[NEWLINE]——埃斯库罗斯"/&gt;</v>
       </c>
     </row>
-    <row r="292" ht="33" spans="1:3">
+    <row r="292" spans="1:3">
       <c r="A292" t="s">
         <v>585</v>
       </c>
@@ -6800,7 +6800,7 @@
         <v>&lt;Replace Tag="LOC_CIVIC_ENVIRONMENTALISM_QUOTE_1" Language="zh_Hans_CN" Text="“我将再度回到日光之下，为你的子孙建造家园。”[NEWLINE]——罗德岛的阿波罗尼奥斯《阿尔戈船英雄纪》"/&gt;</v>
       </c>
     </row>
-    <row r="293" ht="33" spans="1:3">
+    <row r="293" spans="1:3">
       <c r="A293" t="s">
         <v>587</v>
       </c>
@@ -6824,7 +6824,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_BHASA_2_QUOTE" Language="zh_Hans_CN" Text="我的心啊，为你的怀疑终得真相而满意吧。如今，我的陛下已去世，你可得片刻宁静啊。"/&gt;</v>
       </c>
     </row>
-    <row r="295" ht="49.5" spans="1:3">
+    <row r="295" spans="1:3">
       <c r="A295" t="s">
         <v>591</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_MURASAKI_1_QUOTE" Language="zh_Hans_CN" Text="我的哥哥喜德从小开始学习中国古典文学，我非常喜欢听他给我朗读，有些他觉得很难理解和记住的内容，对我而言，却非常容易领会。父亲是个学识渊博的人，他常常感叹到：“真可惜，你为何不是个男孩！”"/&gt;</v>
       </c>
     </row>
-    <row r="296" ht="33" spans="1:3">
+    <row r="296" spans="1:3">
       <c r="A296" t="s">
         <v>593</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_CERVANTES_1_QUOTE" Language="zh_Hans_CN" Text="你可以对此怀疑，但事实如我所言，真相会永远立于谎言之上，正如油永远会漂浮在水面之上。"/&gt;</v>
       </c>
     </row>
-    <row r="298" ht="33" spans="1:3">
+    <row r="298" spans="1:3">
       <c r="A298" t="s">
         <v>597</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_MACHIAVELLI_1_QUOTE" Language="zh_Hans_CN" Text="因此有必要记住，对他人要么利诱，要么除根。人总会报复较小的冒犯；却无法报复沉重的打击；因此，若必犯人，必使其报复无门。"/&gt;</v>
       </c>
     </row>
-    <row r="299" ht="33" spans="1:3">
+    <row r="299" spans="1:3">
       <c r="A299" t="s">
         <v>599</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_PUSHKIN_1_QUOTE" Language="zh_Hans_CN" Text="梦啊，梦啊！你们都去了哪里？你们本多么甜蜜。"/&gt;</v>
       </c>
     </row>
-    <row r="301" ht="33" spans="1:3">
+    <row r="301" spans="1:3">
       <c r="A301" t="s">
         <v>603</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_PUSHKIN_2_QUOTE" Language="zh_Hans_CN" Text="就像办公室里两鬓斑白的地方法官一样，[NEWLINE]他冷静地一并思考了正义[NEWLINE]和不公，冷静地记录下了[NEWLINE]善与恶，全然不带愤怒和同情。"/&gt;</v>
       </c>
     </row>
-    <row r="302" ht="33" spans="1:3">
+    <row r="302" spans="1:3">
       <c r="A302" t="s">
         <v>605</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_POE_1_QUOTE" Language="zh_Hans_CN" Text="“恶棍们！”我大叫起来，“别再掩饰了！我承认这件事！——把地板掀开！这里，这里！——这是他那颗丑陋的心在跳动！”"/&gt;</v>
       </c>
     </row>
-    <row r="303" ht="33" spans="1:3">
+    <row r="303" spans="1:3">
       <c r="A303" t="s">
         <v>607</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_AUSTEN_2_QUOTE" Language="zh_Hans_CN" Text="要知道自己的幸福所在。你只需要耐心。或者，给它一个更迷人的名字——希望。"/&gt;</v>
       </c>
     </row>
-    <row r="306" ht="33" spans="1:3">
+    <row r="306" spans="1:3">
       <c r="A306" t="s">
         <v>613</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_SHELLEY_2_QUOTE" Language="zh_Hans_CN" Text="这个消息将我们从十万年后的天堂带回了当前正遭受苦难的人世。"/&gt;</v>
       </c>
     </row>
-    <row r="308" ht="33" spans="1:3">
+    <row r="308" spans="1:3">
       <c r="A308" t="s">
         <v>617</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_JOYCE_1_QUOTE" Language="zh_Hans_CN" Text="人生由许多天构成，日复一日。我们走遍自己的人生，面对盗贼、鬼魂、巨人、老人、年轻人、妇人、寡妇、相恋的兄弟。但我们一直在面对自己。"/&gt;</v>
       </c>
     </row>
-    <row r="309" ht="33" spans="1:3">
+    <row r="309" spans="1:3">
       <c r="A309" t="s">
         <v>619</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_JOYCE_2_QUOTE" Language="zh_Hans_CN" Text="他们一个个都将变成幽灵。与其任由年龄让我们在忧郁中枯萎憔悴，不如在满怀激情的时候勇敢地跨入另一个世界。"/&gt;</v>
       </c>
     </row>
-    <row r="310" ht="33" spans="1:3">
+    <row r="310" spans="1:3">
       <c r="A310" t="s">
         <v>621</v>
       </c>
@@ -7016,7 +7016,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_TOLSTOY_1_QUOTE" Language="zh_Hans_CN" Text="“皮埃尔说得对，他说人必须相信幸福是有可能的，才能获得幸福，现在我对这点深信不疑。往事不重提，既然我还活着，我就得活下去，活得幸福。”"/&gt;</v>
       </c>
     </row>
-    <row r="311" ht="33" spans="1:3">
+    <row r="311" spans="1:3">
       <c r="A311" t="s">
         <v>623</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_TWAIN_1_QUOTE" Language="zh_Hans_CN" Text="“吉姆说蜜蜂不蛰傻子，但我不信，因为我试过很多次，他们都没蛰我。”"/&gt;</v>
       </c>
     </row>
-    <row r="313" ht="33" spans="1:3">
+    <row r="313" spans="1:3">
       <c r="A313" t="s">
         <v>627</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_TWAIN_2_QUOTE" Language="zh_Hans_CN" Text="他无意中发现了人类行为的一大法则——为了让大人或小孩渴望干什么事，只需设法将这事变得困难就行了。"/&gt;</v>
       </c>
     </row>
-    <row r="314" ht="33" spans="1:3">
+    <row r="314" spans="1:3">
       <c r="A314" t="s">
         <v>629</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_FITZGERALD_2_QUOTE" Language="zh_Hans_CN" Text="她让人为之倾倒——神采奕奕；[NEWLINE]单凭一眼就要理解她的美丽实在是让人苦恼。"/&gt;</v>
       </c>
     </row>
-    <row r="316" ht="33" spans="1:3">
+    <row r="316" spans="1:3">
       <c r="A316" t="s">
         <v>633</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_WELLS_2_QUOTE" Language="zh_Hans_CN" Text="我的阐述简单而足够合理——正如许多错误的理论一样。"/&gt;</v>
       </c>
     </row>
-    <row r="318" ht="33" spans="1:3">
+    <row r="318" spans="1:3">
       <c r="A318" t="s">
         <v>637</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_TAGORE_1_QUOTE" Language="zh_Hans_CN" Text="我非常愿意效忠祖国，但我更崇尚自己拥有的权利，它比我的祖国更重要。把祖国视为神明崇拜会为其带来灾祸。"/&gt;</v>
       </c>
     </row>
-    <row r="319" ht="33" spans="1:3">
+    <row r="319" spans="1:3">
       <c r="A319" t="s">
         <v>639</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_TAGORE_2_QUOTE" Language="zh_Hans_CN" Text="假设有离家的流浪者来到这里仰望夜空，低头聆听黑暗的呢喃，如果我关上门，试图让自己逃出凡尘的束缚，又是谁会在他耳边轻声低语生命的奥秘呢？"/&gt;</v>
       </c>
     </row>
-    <row r="320" ht="33" spans="1:3">
+    <row r="320" spans="1:3">
       <c r="A320" t="s">
         <v>641</v>
       </c>
@@ -7160,7 +7160,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_BEATRIX_POTTER_2_QUOTE" Language="zh_Hans_CN" Text="没有丝线了！"/&gt;</v>
       </c>
     </row>
-    <row r="323" ht="33" spans="1:3">
+    <row r="323" spans="1:3">
       <c r="A323" t="s">
         <v>647</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_RUMI_2_QUOTE" Language="zh_Hans_CN" Text="不掰开面包，何以作为食物？[NEWLINE]不破碎葡萄，何以酿成美酒？"/&gt;</v>
       </c>
     </row>
-    <row r="326" ht="33" spans="1:3">
+    <row r="326" spans="1:3">
       <c r="A326" t="s">
         <v>653</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>&lt;Replace Tag="LOC_GREATWORK_GABRIELA_MISTRAL_1_QUOTE" Language="zh_Hans_CN" Text="真正的大师多少有点艺术家的气质。我们无法接受有人会希望精神领袖成为类似于“职场的老板”或“农场包工头”的角色。"/&gt;</v>
       </c>
     </row>
-    <row r="327" ht="33" spans="1:3">
+    <row r="327" spans="1:3">
       <c r="A327" t="s">
         <v>655</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_PYRAMIDS_QUOTE" Language="zh_Hans_CN" Text="“四十个世纪在这些金字塔的顶端，俯瞰着我们。”[NEWLINE]——拿破仑·波拿巴"/&gt;</v>
       </c>
     </row>
-    <row r="329" ht="33" spans="1:3">
+    <row r="329" spans="1:3">
       <c r="A329" t="s">
         <v>659</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_PETRA_QUOTE" Language="zh_Hans_CN" Text="“佩特拉城是人类工艺的绝妙展示，它把贫瘠的岩石变成了伟大的奇迹。”[NEWLINE]——爱德华·道森"/&gt;</v>
       </c>
     </row>
-    <row r="330" ht="33" spans="1:3">
+    <row r="330" spans="1:3">
       <c r="A330" t="s">
         <v>661</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_MONT_ST_MICHEL_QUOTE" Language="zh_Hans_CN" Text="“教会和国家、灵魂和身体、神和人类，这些都是圣米歇尔山上的一个整体，主要任务是进行战斗，各行其事，或为彼此守卫。”[NEWLINE]——享利·亚当斯"/&gt;</v>
       </c>
     </row>
-    <row r="331" ht="33" spans="1:3">
+    <row r="331" spans="1:3">
       <c r="A331" t="s">
         <v>663</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_CHICHEN_ITZA_QUOTE" Language="zh_Hans_CN" Text="“大蹴球场也让人印象深刻。我很想看他们在这里进行比赛，虽然听说结局很暴力。我认为还是做观众会安全些。”[NEWLINE]——IslaDeb"/&gt;</v>
       </c>
     </row>
-    <row r="332" ht="49.5" spans="1:3">
+    <row r="332" spans="1:3">
       <c r="A332" t="s">
         <v>665</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_STONEHENGE_QUOTE" Language="zh_Hans_CN" Text="“你能想象试图说服600人帮你将一个重为50吨的石头拖动28千米穿过乡村，并用力将它立起来，然后说：‘好了，小伙子们！再推动20块这样的石头…然后就可以庆祝啦！’这样的场景吗？”[NEWLINE]——比尔·布莱森"/&gt;</v>
       </c>
     </row>
-    <row r="333" ht="33" spans="1:3">
+    <row r="333" spans="1:3">
       <c r="A333" t="s">
         <v>667</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_TERRACOTTA_ARMY_QUOTE" Language="zh_Hans_CN" Text="“世界上有七大奇迹，而发现兵马俑也许就是世界第八大奇迹。”[NEWLINE]——雅克·希拉克"/&gt;</v>
       </c>
     </row>
-    <row r="335" ht="33" spans="1:3">
+    <row r="335" spans="1:3">
       <c r="A335" t="s">
         <v>671</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_ALHAMBRA_QUOTE" Language="zh_Hans_CN" Text="“这里的一切似乎都是为了激起友好快乐的感觉，因为一切都如此精致而美丽。”[NEWLINE]——华盛顿·欧文"/&gt;</v>
       </c>
     </row>
-    <row r="336" ht="33" spans="1:3">
+    <row r="336" spans="1:3">
       <c r="A336" t="s">
         <v>673</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_CRISTO_REDENTOR_QUOTE" Language="zh_Hans_CN" Text="“因此，雕塑的作用是让人感到‘一切都掌握在上帝的手中’。”[NEWLINE]——谢尔盖·谢苗诺夫"/&gt;</v>
       </c>
     </row>
-    <row r="337" ht="33" spans="1:3">
+    <row r="337" spans="1:3">
       <c r="A337" t="s">
         <v>675</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_POTALA_PALACE_QUOTE" Language="zh_Hans_CN" Text="“我第一次踏上布达拉宫房顶时，我产生了前所未有也不曾再见的感觉，仿佛步入生命的巅峰一般：整个人进入到从未有过的意识层面之中。”[NEWLINE]——皮柯·耶尔"/&gt;</v>
       </c>
     </row>
-    <row r="338" ht="33" spans="1:3">
+    <row r="338" spans="1:3">
       <c r="A338" t="s">
         <v>677</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_HANGING_GARDENS_QUOTE" Language="zh_Hans_CN" Text="“通过楼梯可以到达顶层，旁边是抽水机，给专门长期雇佣的工人用来从幼发拉底河抽水到花园。”[NEWLINE]——斯特拉波"/&gt;</v>
       </c>
     </row>
-    <row r="339" ht="33" spans="1:3">
+    <row r="339" spans="1:3">
       <c r="A339" t="s">
         <v>679</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_FORBIDDEN_CITY_QUOTE" Language="zh_Hans_CN" Text="“整个宫殿是沿着一条中轴建立的，这也是整个世界的轴心，以宫殿为代表，四个方向的所有东西都是从中心点悬吊下来的。”[NEWLINE]——杰弗里·里格尔"/&gt;</v>
       </c>
     </row>
-    <row r="340" ht="33" spans="1:3">
+    <row r="340" spans="1:3">
       <c r="A340" t="s">
         <v>681</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_EIFFEL_TOWER_QUOTE" Language="zh_Hans_CN" Text="“我应该嫉妒这座塔。她比我更出名。”[NEWLINE]——古斯塔夫·埃菲尔"/&gt;</v>
       </c>
     </row>
-    <row r="342" ht="33" spans="1:3">
+    <row r="342" spans="1:3">
       <c r="A342" t="s">
         <v>685</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_GREAT_LIGHTHOUSE_QUOTE" Language="zh_Hans_CN" Text="“这座灯塔曾是万众瞩目的焦点。”[NEWLINE]——亨利·戴维·梭罗"/&gt;</v>
       </c>
     </row>
-    <row r="344" ht="49.5" spans="1:3">
+    <row r="344" spans="1:3">
       <c r="A344" t="s">
         <v>689</v>
       </c>
@@ -7424,7 +7424,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_SYDNEY_OPERA_HOUSE_QUOTE" Language="zh_Hans_CN" Text="“在幕布拉起前很久，歌剧已经开始，在幕布降下后很久，歌剧才结束。它开始于我的想象中，变成了我的生命，在我离开歌剧院很久之后，它依然是我生活的一部分。”[NEWLINE]——玛丽亚·卡拉斯"/&gt;</v>
       </c>
     </row>
-    <row r="345" ht="33" spans="1:3">
+    <row r="345" spans="1:3">
       <c r="A345" t="s">
         <v>691</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_BIG_BEN_QUOTE" Language="zh_Hans_CN" Text="“不要盯着大钟看；要做大钟正在做的事。继续前进。”[NEWLINE]——萨姆·李文森"/&gt;</v>
       </c>
     </row>
-    <row r="347" ht="33" spans="1:3">
+    <row r="347" spans="1:3">
       <c r="A347" t="s">
         <v>695</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_COLOSSEUM_QUOTE" Language="zh_Hans_CN" Text="“竞技场耸立，罗马便耸立；竞技场倒塌，罗马便倒塌；罗马倒塌，世界便倒塌。”[NEWLINE]——圣徒比德"/&gt;</v>
       </c>
     </row>
-    <row r="348" ht="33" spans="1:3">
+    <row r="348" spans="1:3">
       <c r="A348" t="s">
         <v>697</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_ESTADIO_DO_MARACANA_QUOTE" Language="zh_Hans_CN" Text="“纵观历史，只有三个人能让马拉卡纳球场安静下来：教皇、法兰克·辛纳屈、我。”[NEWLINE]——阿尔喀德斯·吉贾（乌拉圭足球运动员）"/&gt;</v>
       </c>
     </row>
-    <row r="349" ht="33" spans="1:3">
+    <row r="349" spans="1:3">
       <c r="A349" t="s">
         <v>699</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_VENETIAN_ARSENAL_QUOTE" Language="zh_Hans_CN" Text="“威尼斯联邦的军械库上有这样一段题词：‘快乐就是城市在和平时期思考战争。’”[NEWLINE]——罗伯特·伯顿"/&gt;</v>
       </c>
     </row>
-    <row r="350" ht="33" spans="1:3">
+    <row r="350" spans="1:3">
       <c r="A350" t="s">
         <v>701</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_RUHR_VALLEY_QUOTE" Language="zh_Hans_CN" Text="“德国的工业中心实际已停止了运营。几乎没有人工作，几乎没有任何东西在运行；鲁尔地区的全体居民…需要这个国家其它地方的援助。”[NEWLINE]——亚当·弗格森"/&gt;</v>
       </c>
     </row>
-    <row r="351" ht="33" spans="1:3">
+    <row r="351" spans="1:3">
       <c r="A351" t="s">
         <v>703</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_MAHABODHI_TEMPLE_QUOTE" Language="zh_Hans_CN" Text="“在印度比哈尔邦尘土飞扬的喧闹角落里，有一个神奇的地方被人们当作佛教中心。”[NEWLINE]——菩提伽耶游客指南"/&gt;</v>
       </c>
     </row>
-    <row r="352" ht="49.5" spans="1:3">
+    <row r="352" spans="1:3">
       <c r="A352" t="s">
         <v>705</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_HAGIA_SOPHIA_QUOTE" Language="zh_Hans_CN" Text="“它是一座华丽的重要纪念碑，是跨文化宝藏…除非和直到它能被两种宗教和谐共享——这真是一个伟大的想法——它应该继续作为一座世俗建筑，同时敬奉两种让它如此华丽的宗教。”[NEWLINE]——牛博·武约维奇"/&gt;</v>
       </c>
     </row>
-    <row r="353" ht="33" spans="1:3">
+    <row r="353" spans="1:3">
       <c r="A353" t="s">
         <v>707</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_GREAT_LIBRARY_QUOTE" Language="zh_Hans_CN" Text="“我们可以徜徉在亚历山大图书馆密密麻麻的书架前，这是想象力和知识的聚集地；它的毁灭是一种警告，让我们意识到我们所拥有的一切都将消失。”[NEWLINE]——阿尔维托·曼古埃尔"/&gt;</v>
       </c>
     </row>
-    <row r="354" ht="33" spans="1:3">
+    <row r="354" spans="1:3">
       <c r="A354" t="s">
         <v>709</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_OXFORD_UNIVERSITY_QUOTE" Language="zh_Hans_CN" Text="“牛津大学的聪明人…知道所有需要知道的事。[NEWLINE]但他们都没有蟾蜍先生一半聪明！”[NEWLINE]——肯尼思·格拉姆"/&gt;</v>
       </c>
     </row>
-    <row r="355" ht="49.5" spans="1:3">
+    <row r="355" spans="1:3">
       <c r="A355" t="s">
         <v>711</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_BIOSHPERE_QUOTE" Language="zh_Hans_CN" Text="“天堂既在我们头顶，也在我们脚下。”[NEWLINE]——亨利·戴维·梭罗"/&gt;</v>
       </c>
     </row>
-    <row r="358" ht="33" spans="1:3">
+    <row r="358" spans="1:3">
       <c r="A358" t="s">
         <v>717</v>
       </c>
@@ -7589,10 +7589,10 @@
       </c>
       <c r="C358" t="str">
         <f t="shared" si="5"/>
-        <v>&lt;Replace Tag="LOC_BUILDING_AMUNDSEN_SCOTT_RESEARCH_STATION_QUOTE" Language="zh_Hans_CN" Text="论科学领导力，斯科特首屈一指；而论行进之迅速高效，阿蒙森当仁不让。[NEWLINE]——雷蒙德·普里斯特利爵士"/&gt;</v>
-      </c>
-    </row>
-    <row r="359" ht="33" spans="1:3">
+        <v>&lt;Replace Tag="LOC_BUILDING_AMUNDSEN_SCOTT_RESEARCH_STATION_QUOTE" Language="zh_Hans_CN" Text="“论科学领导力，斯科特首屈一指；而论行进之迅速高效，阿蒙森当仁不让。”[NEWLINE]——雷蒙德·普里斯特利爵士"/&gt;</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
       <c r="A359" t="s">
         <v>719</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_CASA_DE_CONTRATACION_QUOTE" Language="zh_Hans_CN" Text="“西方国境外发现的所有领土均隶属于卡斯蒂利亚国王、王后，及其子孙后代。”[NEWLINE]——《托尔德西里亚斯条约》"/&gt;</v>
       </c>
     </row>
-    <row r="360" ht="33" spans="1:3">
+    <row r="360" spans="1:3">
       <c r="A360" t="s">
         <v>721</v>
       </c>
@@ -7616,7 +7616,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_KILWA_KISIWANI_QUOTE" Language="zh_Hans_CN" Text="“基尔瓦是世界上建设得最为美丽的城市之一。房屋均为木制结构，房顶由草绳铺成，雨后生机勃勃。”[NEWLINE]——伊本·白图泰"/&gt;</v>
       </c>
     </row>
-    <row r="361" ht="33" spans="1:3">
+    <row r="361" spans="1:3">
       <c r="A361" t="s">
         <v>723</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_KOTOKU_IN_QUOTE" Language="zh_Hans_CN" Text="“踏过蜿蜒的羊肠小道，穿过地狱烈焰迎接审判日的人啊，请静观异教徒的祈祷，向着那镰仓大佛！”[NEWLINE]——鲁德亚德·吉卜林"/&gt;</v>
       </c>
     </row>
-    <row r="362" ht="33" spans="1:3">
+    <row r="362" spans="1:3">
       <c r="A362" t="s">
         <v>725</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_ST_BASILS_CATHEDRAL_QUOTE" Language="zh_Hans_CN" Text="“第一个设计成扭转的造型，红绿相间；另一个有刺角，有黄有黑；第三个装饰了一片片蓝色和深红色；第四个有点像个蜜瓜。”[NEWLINE]——凯瑟琳·布兰奇·格思里"/&gt;</v>
       </c>
     </row>
-    <row r="363" ht="33" spans="1:3">
+    <row r="363" spans="1:3">
       <c r="A363" t="s">
         <v>727</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_STATUE_LIBERTY_QUOTE" Language="zh_Hans_CN" Text="“海水冲刷，落日掩映，国门之处将立有一巨大女子，手执火炬，以禁锢的雷电为火。”[NEWLINE]——艾玛·拉撒路"/&gt;</v>
       </c>
     </row>
-    <row r="364" ht="33" spans="1:3">
+    <row r="364" spans="1:3">
       <c r="A364" t="s">
         <v>729</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_TAJ_MAHAL_QUOTE" Language="zh_Hans_CN" Text="“你建造过空中城堡吗？此物只应天上有，下凡人间便为岁月奇观。”[NEWLINE]——贝亚德·泰勒"/&gt;</v>
       </c>
     </row>
-    <row r="365" ht="49.5" spans="1:3">
+    <row r="365" spans="1:3">
       <c r="A365" t="s">
         <v>731</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_TEMPLE_OF_ARTEMIS_QUOTE" Language="zh_Hans_CN" Text="“我看到耸入云霄的阿耳忒弥斯神庙后，其他建筑奇观皆黯然失色。我不禁叹道：‘看呐！除了在众神所居的奥林匹斯山之外，太阳从未显得如此宏大壮观。’”[NEWLINE]——西顿的安提帕特"/&gt;</v>
       </c>
     </row>
-    <row r="366" ht="33" spans="1:3">
+    <row r="366" spans="1:3">
       <c r="A366" t="s">
         <v>733</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_GOLDEN_GATE_BRIDGE_QUOTE" Language="zh_Hans_CN" Text="“美梦金门徐徐而开，[NEWLINE]英雄美人相识相爱。[NEWLINE]炬火照亮连理风采，[NEWLINE]仿若星光洒落晴海！”[NEWLINE]——珀西·比希·雪莱"/&gt;</v>
       </c>
     </row>
-    <row r="367" ht="49.5" spans="1:3">
+    <row r="367" spans="1:3">
       <c r="A367" t="s">
         <v>735</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_GREAT_BATH_QUOTE" Language="zh_Hans_CN" Text="“就算落入的是无情的滤筛，[NEWLINE]我仍愿意将我的爱情之水倾泻倒下。[NEWLINE]纵使白费，也在所不惜。如印度人一般，[NEWLINE]虔诚信仰又执迷不悟。[NEWLINE]我崇拜着太阳，阳光普照信徒，[NEWLINE]但却不知一人为它痴狂。”[NEWLINE]——威廉·莎士比亚"/&gt;</v>
       </c>
     </row>
-    <row r="368" ht="33" spans="1:3">
+    <row r="368" spans="1:3">
       <c r="A368" t="s">
         <v>737</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_MACHU_PICCHU_QUOTE" Language="zh_Hans_CN" Text="“…苍鹰翱翔，高塔环绕，直入云霄威风堂堂；[NEWLINE]眼中城墙，斑驳残破已成过往，[NEWLINE]所猎之物，无处可躲尸骨埋葬。”[NEWLINE]——萨缪尔·普劳特·希尔"/&gt;</v>
       </c>
     </row>
-    <row r="369" ht="49.5" spans="1:3">
+    <row r="369" spans="1:3">
       <c r="A369" t="s">
         <v>739</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_ORSZAGHAZ_QUOTE" Language="zh_Hans_CN" Text="“有自治的地方便有自由，有自由的地方则有公正与爱国之心。”[NEWLINE]——科苏特·拉约什"/&gt;</v>
       </c>
     </row>
-    <row r="371" ht="33" spans="1:3">
+    <row r="371" spans="1:3">
       <c r="A371" t="s">
         <v>743</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_PANAMA_CANAL_QUOTE" Language="zh_Hans_CN" Text="“所以，地虽改变，山虽摇动到海心，其中的水虽澎湃翻腾，山虽因海涨而战抖，我们也不害怕。”[NEWLINE]——《诗篇》 46:2-3"/&gt;</v>
       </c>
     </row>
-    <row r="372" ht="33" spans="1:3">
+    <row r="372" spans="1:3">
       <c r="A372" t="s">
         <v>745</v>
       </c>
@@ -7760,7 +7760,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_UNIVERSITY_SANKORE_QUOTE" Language="zh_Hans_CN" Text="“学者皆是先知的子嗣。先知并未在世间留下任何财富，而是将宝贵的知识传给后人。”[NEWLINE]——《巴扎尔圣训集》10/68"/&gt;</v>
       </c>
     </row>
-    <row r="373" ht="33" spans="1:3">
+    <row r="373" spans="1:3">
       <c r="A373" t="s">
         <v>747</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_ANGKOR_WAT_QUOTE" Language="zh_Hans_CN" Text="“这座寺庙四周环绕着护城河，须借助唯一的桥梁进出，门口有两只威风凛凛的巨型石虎镇守，似乎要把恐惧植入来访者的心中。”[NEWLINE]——蒂欧格·都·科托"/&gt;</v>
       </c>
     </row>
-    <row r="374" ht="33" spans="1:3">
+    <row r="374" spans="1:3">
       <c r="A374" t="s">
         <v>749</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_HALICARNASSUS_MAUSOLEUM_QUOTE" Language="zh_Hans_CN" Text="“在哈利卡纳苏斯坐落着一个巨大的陵墓，它的规模和壮丽令其它亡魂都不敢叫嚣。”[NEWLINE]——萨莫萨塔的琉善"/&gt;</v>
       </c>
     </row>
-    <row r="375" ht="33" spans="1:3">
+    <row r="375" spans="1:3">
       <c r="A375" t="s">
         <v>751</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>&lt;Replace Tag="LOC_BUILDING_APADANA_QUOTE" Language="zh_Hans_CN" Text="“我的祖先大流士一世修建了这座阿帕达纳宫，但它却被无情烧毁。托阿胡拉马兹达、阿娜希塔和密特拉的鸿福，我让它重见天日。”[NEWLINE]——阿尔塔薛西斯二世"/&gt;</v>
       </c>
     </row>
-    <row r="376" ht="33" spans="1:3">
+    <row r="376" spans="1:3">
       <c r="A376" t="s">
         <v>753</v>
       </c>
